--- a/InputData/ccs/CCSTaSC/CCS Transportation and Storage Cost.xlsx
+++ b/InputData/ccs/CCSTaSC/CCS Transportation and Storage Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\CCSTaSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\CCSTaSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB69C57-C5D6-459F-AF6B-9308998FBC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C928A-3AAF-49BE-9925-7B059DEE51E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21525" yWindow="2850" windowWidth="21600" windowHeight="12675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
     <t>Value from study (2021 $)</t>
   </si>
   <si>
-    <t>2021 to 2012 $</t>
+    <t>2018 to 2012 $</t>
   </si>
 </sst>
 </file>
@@ -123,7 +123,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -137,7 +137,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -478,7 +477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
@@ -496,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -504,12 +503,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0.84699999999999998</v>
+        <v>0.9143273584567535</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{E6E6B16C-F4E4-4E8F-9F7E-3FD9DA689F40}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -621,125 +623,125 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="C2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="D2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="E2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="F2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="G2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="H2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="I2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="J2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="K2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="L2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="M2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="N2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="O2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="P2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="Q2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="R2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="S2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="T2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="U2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="V2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="W2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="X2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="Y2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="Z2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="AA2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="AB2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="AC2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="AD2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
-      </c>
-      <c r="AE2" s="7">
-        <f>About!$B$10*About!$B$11</f>
-        <v>14.398999999999999</v>
+      <c r="B2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="C2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="D2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="E2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="F2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="G2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="H2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="I2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="J2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="K2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="L2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="M2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="N2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="O2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="P2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="Q2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="R2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="S2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="T2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="U2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="V2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="W2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="X2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="Y2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="Z2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="AA2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="AB2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="AC2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="AD2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
+      </c>
+      <c r="AE2">
+        <f>About!$B$10*About!$B$11</f>
+        <v>21.02952924450533</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">

--- a/InputData/ccs/CCSTaSC/CCS Transportation and Storage Cost.xlsx
+++ b/InputData/ccs/CCSTaSC/CCS Transportation and Storage Cost.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27618"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\CCSTaSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\CCSTaSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C928A-3AAF-49BE-9925-7B059DEE51E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9333C42D-0F53-421E-B2A4-19E44269A3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21525" yWindow="2850" windowWidth="21600" windowHeight="12675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="CCSTaSC" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -25,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,16 +39,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>CCS Transportation and Storage Cost</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
     <t>Current Value and Infrastructure Investment and Jobs Act Effects</t>
-  </si>
-  <si>
-    <t>Slide 38</t>
-  </si>
-  <si>
-    <t>https://netzeroamerica.princeton.edu/img/Princeton%20NZA%20FINAL%20REPORT%20SUMMARY%20(29Oct2021).pdf</t>
   </si>
   <si>
     <t>Princeton University</t>
@@ -52,16 +54,19 @@
     <t>Net-Zero America: Potential Pathways, Infrastructure, and Impacts</t>
   </si>
   <si>
-    <t>CCS Transportation and Storage Cost</t>
+    <t>https://netzeroamerica.princeton.edu/img/Princeton%20NZA%20FINAL%20REPORT%20SUMMARY%20(29Oct2021).pdf</t>
   </si>
   <si>
-    <t>Transportation and Storage Cost ($ per metric ton CO2)</t>
+    <t>Slide 38</t>
   </si>
   <si>
     <t>Value from study (2021 $)</t>
   </si>
   <si>
-    <t>2018 to 2012 $</t>
+    <t>2021 to 2012 $</t>
+  </si>
+  <si>
+    <t>Transportation and Storage Cost ($ per metric ton CO2)</t>
   </si>
 </sst>
 </file>
@@ -71,7 +76,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,75 +448,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
     <col min="2" max="2" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="5">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="30">
       <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
       <c r="B11">
-        <v>0.9143273584567535</v>
+        <v>0.84699999999999998</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{E6E6B16C-F4E4-4E8F-9F7E-3FD9DA689F40}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -521,13 +523,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47.140625" customWidth="1"/>
     <col min="2" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -619,135 +621,296 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="C2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="D2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="E2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="F2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="G2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="H2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="I2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="J2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="K2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="L2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="M2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="N2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="O2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="P2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="Q2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="R2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="S2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="T2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="U2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="V2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="W2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="X2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="Y2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="Z2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="AA2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="AB2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="AC2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="AD2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="AE2">
         <f>About!$B$10*About!$B$11</f>
-        <v>21.02952924450533</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+        <v>14.398999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="K4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49383CDA-513F-4C6F-8698-04BE394C25F8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1880C574-07B6-4562-9518-A9688D565C4F}"/>
 </file>